--- a/data/nzd0036/nzd0036.xlsx
+++ b/data/nzd0036/nzd0036.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N569"/>
+  <dimension ref="A1:N570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27748,6 +27748,54 @@
         <v>354.75</v>
       </c>
       <c r="N569" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>362.38</v>
+      </c>
+      <c r="C570" t="n">
+        <v>357.44</v>
+      </c>
+      <c r="D570" t="n">
+        <v>338.31</v>
+      </c>
+      <c r="E570" t="n">
+        <v>343.47</v>
+      </c>
+      <c r="F570" t="n">
+        <v>348.8</v>
+      </c>
+      <c r="G570" t="n">
+        <v>341.63</v>
+      </c>
+      <c r="H570" t="n">
+        <v>341.04</v>
+      </c>
+      <c r="I570" t="n">
+        <v>345.02</v>
+      </c>
+      <c r="J570" t="n">
+        <v>348.86</v>
+      </c>
+      <c r="K570" t="n">
+        <v>350.16</v>
+      </c>
+      <c r="L570" t="n">
+        <v>346.96</v>
+      </c>
+      <c r="M570" t="n">
+        <v>351.56</v>
+      </c>
+      <c r="N570" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27764,7 +27812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B578"/>
+  <dimension ref="A1:B579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33547,6 +33595,16 @@
       </c>
       <c r="B578" t="n">
         <v>-0.23</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -33715,28 +33773,28 @@
         <v>0.07480000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3258140579498674</v>
+        <v>0.3220672541126459</v>
       </c>
       <c r="J2" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K2" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1572177125657378</v>
+        <v>0.1539322639498799</v>
       </c>
       <c r="M2" t="n">
-        <v>4.39467756394568</v>
+        <v>4.40879036280141</v>
       </c>
       <c r="N2" t="n">
-        <v>32.16339860054456</v>
+        <v>32.29979621221848</v>
       </c>
       <c r="O2" t="n">
-        <v>5.671278392086264</v>
+        <v>5.683290966703929</v>
       </c>
       <c r="P2" t="n">
-        <v>364.309232852477</v>
+        <v>364.3463310389574</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33793,28 +33851,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4918312081629289</v>
+        <v>0.4897508371885171</v>
       </c>
       <c r="J3" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K3" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3963595360002106</v>
+        <v>0.394633179593037</v>
       </c>
       <c r="M3" t="n">
-        <v>3.442468833220604</v>
+        <v>3.447687453354809</v>
       </c>
       <c r="N3" t="n">
-        <v>20.82234159045194</v>
+        <v>20.84522347272478</v>
       </c>
       <c r="O3" t="n">
-        <v>4.56315040191006</v>
+        <v>4.565656959597905</v>
       </c>
       <c r="P3" t="n">
-        <v>350.3235189779558</v>
+        <v>350.3441173315687</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33871,28 +33929,28 @@
         <v>0.1005</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4783007431525572</v>
+        <v>0.4716083896824486</v>
       </c>
       <c r="J4" t="n">
+        <v>569</v>
+      </c>
+      <c r="K4" t="n">
         <v>568</v>
       </c>
-      <c r="K4" t="n">
-        <v>567</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1287605256043733</v>
+        <v>0.1253157045516968</v>
       </c>
       <c r="M4" t="n">
-        <v>7.617743117804863</v>
+        <v>7.640238236699029</v>
       </c>
       <c r="N4" t="n">
-        <v>87.04583291034142</v>
+        <v>87.50352308868989</v>
       </c>
       <c r="O4" t="n">
-        <v>9.329835631475049</v>
+        <v>9.354331782051025</v>
       </c>
       <c r="P4" t="n">
-        <v>344.3988790871095</v>
+        <v>344.4654097975302</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33949,28 +34007,28 @@
         <v>0.1076</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4766225843581788</v>
+        <v>0.4707311132610617</v>
       </c>
       <c r="J5" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K5" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1463343147076923</v>
+        <v>0.1429787594585866</v>
       </c>
       <c r="M5" t="n">
-        <v>7.06669746251362</v>
+        <v>7.082932946491828</v>
       </c>
       <c r="N5" t="n">
-        <v>74.9030064114658</v>
+        <v>75.24835900258168</v>
       </c>
       <c r="O5" t="n">
-        <v>8.654652298704194</v>
+        <v>8.674581200414329</v>
       </c>
       <c r="P5" t="n">
-        <v>347.4491131196178</v>
+        <v>347.5074462757959</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34027,28 +34085,28 @@
         <v>0.0897</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4487491513720334</v>
+        <v>0.4435486909797138</v>
       </c>
       <c r="J6" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K6" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1460204768057134</v>
+        <v>0.1429579035838021</v>
       </c>
       <c r="M6" t="n">
-        <v>6.482824695120927</v>
+        <v>6.495355843947038</v>
       </c>
       <c r="N6" t="n">
-        <v>66.56552235511163</v>
+        <v>66.82019690747579</v>
       </c>
       <c r="O6" t="n">
-        <v>8.158769659397894</v>
+        <v>8.174362171293598</v>
       </c>
       <c r="P6" t="n">
-        <v>351.5683904638873</v>
+        <v>351.619881723585</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34105,28 +34163,28 @@
         <v>0.0914</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4061822814557141</v>
+        <v>0.4006908887491056</v>
       </c>
       <c r="J7" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K7" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1276025970114431</v>
+        <v>0.1243436916325691</v>
       </c>
       <c r="M7" t="n">
-        <v>6.29090213479039</v>
+        <v>6.3068026394607</v>
       </c>
       <c r="N7" t="n">
-        <v>63.75366685159272</v>
+        <v>64.05603046735493</v>
       </c>
       <c r="O7" t="n">
-        <v>7.984589335187673</v>
+        <v>8.003501138086689</v>
       </c>
       <c r="P7" t="n">
-        <v>346.3378739070104</v>
+        <v>346.3922457715429</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34183,28 +34241,28 @@
         <v>0.0832</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3344575034525787</v>
+        <v>0.328925727854669</v>
       </c>
       <c r="J8" t="n">
+        <v>569</v>
+      </c>
+      <c r="K8" t="n">
         <v>568</v>
       </c>
-      <c r="K8" t="n">
-        <v>567</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.08800947601800513</v>
+        <v>0.08518929972046041</v>
       </c>
       <c r="M8" t="n">
-        <v>6.390541396917485</v>
+        <v>6.405819313525508</v>
       </c>
       <c r="N8" t="n">
-        <v>65.623406413464</v>
+        <v>65.92929357795764</v>
       </c>
       <c r="O8" t="n">
-        <v>8.10082751411632</v>
+        <v>8.119685559056929</v>
       </c>
       <c r="P8" t="n">
-        <v>347.7546028882446</v>
+        <v>347.80934184361</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34261,28 +34319,28 @@
         <v>0.0833</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2806942949532582</v>
+        <v>0.2758256378391707</v>
       </c>
       <c r="J9" t="n">
+        <v>569</v>
+      </c>
+      <c r="K9" t="n">
         <v>568</v>
       </c>
-      <c r="K9" t="n">
-        <v>567</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.07701495156903104</v>
+        <v>0.074426967808498</v>
       </c>
       <c r="M9" t="n">
-        <v>5.825362585566552</v>
+        <v>5.836659454013224</v>
       </c>
       <c r="N9" t="n">
-        <v>53.45677852185373</v>
+        <v>53.68910629079349</v>
       </c>
       <c r="O9" t="n">
-        <v>7.311414262771173</v>
+        <v>7.327285055925795</v>
       </c>
       <c r="P9" t="n">
-        <v>351.2877964228412</v>
+        <v>351.3359735767658</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34339,28 +34397,28 @@
         <v>0.0867</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2909071312657652</v>
+        <v>0.2859534530133855</v>
       </c>
       <c r="J10" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K10" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1070037101352209</v>
+        <v>0.1033650313182781</v>
       </c>
       <c r="M10" t="n">
-        <v>5.085677012981881</v>
+        <v>5.098202517714297</v>
       </c>
       <c r="N10" t="n">
-        <v>39.91792173204468</v>
+        <v>40.18499198856045</v>
       </c>
       <c r="O10" t="n">
-        <v>6.318063131375364</v>
+        <v>6.339163350834276</v>
       </c>
       <c r="P10" t="n">
-        <v>355.0958793166457</v>
+        <v>355.1449271151308</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34417,28 +34475,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.240333467195764</v>
+        <v>0.2360998093541173</v>
       </c>
       <c r="J11" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K11" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0749317074289928</v>
+        <v>0.07237104619731416</v>
       </c>
       <c r="M11" t="n">
-        <v>5.029859306348901</v>
+        <v>5.040957359139057</v>
       </c>
       <c r="N11" t="n">
-        <v>40.30371129573867</v>
+        <v>40.47919633576164</v>
       </c>
       <c r="O11" t="n">
-        <v>6.348520402088873</v>
+        <v>6.36232633049906</v>
       </c>
       <c r="P11" t="n">
-        <v>355.7018682144005</v>
+        <v>355.7437868829318</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34495,28 +34553,28 @@
         <v>0.0506</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4670681532442648</v>
+        <v>0.4626710078907418</v>
       </c>
       <c r="J12" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K12" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1988552573547803</v>
+        <v>0.1956649386174476</v>
       </c>
       <c r="M12" t="n">
-        <v>5.489107169059213</v>
+        <v>5.500026707360471</v>
       </c>
       <c r="N12" t="n">
-        <v>49.67556218739733</v>
+        <v>49.8539674643401</v>
       </c>
       <c r="O12" t="n">
-        <v>7.048089257905105</v>
+        <v>7.060734201507667</v>
       </c>
       <c r="P12" t="n">
-        <v>346.9994925451802</v>
+        <v>347.0430299507647</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34573,28 +34631,28 @@
         <v>0.0723</v>
       </c>
       <c r="I13" t="n">
-        <v>0.688949256091685</v>
+        <v>0.6868494363385812</v>
       </c>
       <c r="J13" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K13" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2528023984857796</v>
+        <v>0.2522876146668862</v>
       </c>
       <c r="M13" t="n">
-        <v>6.880664565402864</v>
+        <v>6.878735668942551</v>
       </c>
       <c r="N13" t="n">
-        <v>78.09094627715432</v>
+        <v>78.01205330529319</v>
       </c>
       <c r="O13" t="n">
-        <v>8.836908185398007</v>
+        <v>8.832443224006209</v>
       </c>
       <c r="P13" t="n">
-        <v>339.2337988764467</v>
+        <v>339.2548598229504</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34632,7 +34690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N569"/>
+  <dimension ref="A1:N570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75575,6 +75633,78 @@
         </is>
       </c>
     </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>-34.96168842972593,173.6701779191743</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>-34.96167007467426,173.67107871321065</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>-34.96175624255627,173.67201763723804</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>-34.96150260324341,173.67289185184072</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>-34.96122065481134,173.6737398401976</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>-34.96092498074637,173.6745827981734</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>-34.960573351023186,173.67537927983082</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>-34.9601555564371,173.67613675692766</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>-34.959687029299126,173.6768529031805</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>-34.95913268051721,173.67748225964536</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>-34.95851551266971,173.6780312389263</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>-34.95780635049073,173.6783177155763</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0036/nzd0036.xlsx
+++ b/data/nzd0036/nzd0036.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N570"/>
+  <dimension ref="A1:N573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27796,6 +27796,150 @@
         <v>351.56</v>
       </c>
       <c r="N570" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>362.35</v>
+      </c>
+      <c r="C571" t="n">
+        <v>358.38</v>
+      </c>
+      <c r="D571" t="n">
+        <v>338.89</v>
+      </c>
+      <c r="E571" t="n">
+        <v>344.15</v>
+      </c>
+      <c r="F571" t="n">
+        <v>349.55</v>
+      </c>
+      <c r="G571" t="n">
+        <v>342.73</v>
+      </c>
+      <c r="H571" t="n">
+        <v>342.38</v>
+      </c>
+      <c r="I571" t="n">
+        <v>346.67</v>
+      </c>
+      <c r="J571" t="n">
+        <v>350.89</v>
+      </c>
+      <c r="K571" t="n">
+        <v>352.25</v>
+      </c>
+      <c r="L571" t="n">
+        <v>346.97</v>
+      </c>
+      <c r="M571" t="n">
+        <v>351.7</v>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>361.48</v>
+      </c>
+      <c r="C572" t="n">
+        <v>357.58</v>
+      </c>
+      <c r="D572" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="E572" t="n">
+        <v>344.7</v>
+      </c>
+      <c r="F572" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="G572" t="n">
+        <v>343.37</v>
+      </c>
+      <c r="H572" t="n">
+        <v>342.69</v>
+      </c>
+      <c r="I572" t="n">
+        <v>347.07</v>
+      </c>
+      <c r="J572" t="n">
+        <v>351.72</v>
+      </c>
+      <c r="K572" t="n">
+        <v>353.05</v>
+      </c>
+      <c r="L572" t="n">
+        <v>348.27</v>
+      </c>
+      <c r="M572" t="n">
+        <v>352.71</v>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>361.48</v>
+      </c>
+      <c r="C573" t="n">
+        <v>357.58</v>
+      </c>
+      <c r="D573" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="E573" t="n">
+        <v>344.7</v>
+      </c>
+      <c r="F573" t="n">
+        <v>349.82</v>
+      </c>
+      <c r="G573" t="n">
+        <v>343.51</v>
+      </c>
+      <c r="H573" t="n">
+        <v>343.41</v>
+      </c>
+      <c r="I573" t="n">
+        <v>347.07</v>
+      </c>
+      <c r="J573" t="n">
+        <v>351.72</v>
+      </c>
+      <c r="K573" t="n">
+        <v>353.05</v>
+      </c>
+      <c r="L573" t="n">
+        <v>348.27</v>
+      </c>
+      <c r="M573" t="n">
+        <v>352.71</v>
+      </c>
+      <c r="N573" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27812,7 +27956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B579"/>
+  <dimension ref="A1:B582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33605,6 +33749,36 @@
       </c>
       <c r="B579" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -33773,28 +33947,28 @@
         <v>0.07480000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3220672541126459</v>
+        <v>0.3103690912288594</v>
       </c>
       <c r="J2" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K2" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1539322639498799</v>
+        <v>0.1436498374845279</v>
       </c>
       <c r="M2" t="n">
-        <v>4.40879036280141</v>
+        <v>4.454057097358781</v>
       </c>
       <c r="N2" t="n">
-        <v>32.29979621221848</v>
+        <v>32.76305720923868</v>
       </c>
       <c r="O2" t="n">
-        <v>5.683290966703929</v>
+        <v>5.723902271111788</v>
       </c>
       <c r="P2" t="n">
-        <v>364.3463310389574</v>
+        <v>364.4624560365594</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33851,28 +34025,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4897508371885171</v>
+        <v>0.4840271394562704</v>
       </c>
       <c r="J3" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K3" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L3" t="n">
-        <v>0.394633179593037</v>
+        <v>0.390214461856736</v>
       </c>
       <c r="M3" t="n">
-        <v>3.447687453354809</v>
+        <v>3.460756112859869</v>
       </c>
       <c r="N3" t="n">
-        <v>20.84522347272478</v>
+        <v>20.88788325288658</v>
       </c>
       <c r="O3" t="n">
-        <v>4.565656959597905</v>
+        <v>4.570326383628043</v>
       </c>
       <c r="P3" t="n">
-        <v>350.3441173315687</v>
+        <v>350.4009360612212</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33929,28 +34103,28 @@
         <v>0.1005</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4716083896824486</v>
+        <v>0.4530561758558001</v>
       </c>
       <c r="J4" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K4" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1253157045516968</v>
+        <v>0.1161966356917317</v>
       </c>
       <c r="M4" t="n">
-        <v>7.640238236699029</v>
+        <v>7.702595765033617</v>
       </c>
       <c r="N4" t="n">
-        <v>87.50352308868989</v>
+        <v>88.62194501769247</v>
       </c>
       <c r="O4" t="n">
-        <v>9.354331782051025</v>
+        <v>9.413922934552442</v>
       </c>
       <c r="P4" t="n">
-        <v>344.4654097975302</v>
+        <v>344.6503103255982</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34007,28 +34181,28 @@
         <v>0.1076</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4707311132610617</v>
+        <v>0.4544490314446161</v>
       </c>
       <c r="J5" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K5" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1429787594585866</v>
+        <v>0.1341083216941211</v>
       </c>
       <c r="M5" t="n">
-        <v>7.082932946491828</v>
+        <v>7.125055181574965</v>
       </c>
       <c r="N5" t="n">
-        <v>75.24835900258168</v>
+        <v>76.07806326224346</v>
       </c>
       <c r="O5" t="n">
-        <v>8.674581200414329</v>
+        <v>8.722273973124409</v>
       </c>
       <c r="P5" t="n">
-        <v>347.5074462757959</v>
+        <v>347.6690706406049</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34085,28 +34259,28 @@
         <v>0.0897</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4435486909797138</v>
+        <v>0.4292489121799142</v>
       </c>
       <c r="J6" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K6" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1429579035838021</v>
+        <v>0.1349010089637369</v>
       </c>
       <c r="M6" t="n">
-        <v>6.495355843947038</v>
+        <v>6.526424140940757</v>
       </c>
       <c r="N6" t="n">
-        <v>66.82019690747579</v>
+        <v>67.41402527906888</v>
       </c>
       <c r="O6" t="n">
-        <v>8.174362171293598</v>
+        <v>8.210604440543271</v>
       </c>
       <c r="P6" t="n">
-        <v>351.619881723585</v>
+        <v>351.7618290489261</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34163,28 +34337,28 @@
         <v>0.0914</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4006908887491056</v>
+        <v>0.3861541303717587</v>
       </c>
       <c r="J7" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K7" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1243436916325691</v>
+        <v>0.1162167343395519</v>
       </c>
       <c r="M7" t="n">
-        <v>6.3068026394607</v>
+        <v>6.345126355629898</v>
       </c>
       <c r="N7" t="n">
-        <v>64.05603046735493</v>
+        <v>64.69634123437916</v>
       </c>
       <c r="O7" t="n">
-        <v>8.003501138086689</v>
+        <v>8.043403585198194</v>
       </c>
       <c r="P7" t="n">
-        <v>346.3922457715429</v>
+        <v>346.5365446213379</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34241,28 +34415,28 @@
         <v>0.0832</v>
       </c>
       <c r="I8" t="n">
-        <v>0.328925727854669</v>
+        <v>0.3144962917613515</v>
       </c>
       <c r="J8" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K8" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08518929972046041</v>
+        <v>0.07828483247491103</v>
       </c>
       <c r="M8" t="n">
-        <v>6.405819313525508</v>
+        <v>6.441535284924391</v>
       </c>
       <c r="N8" t="n">
-        <v>65.92929357795764</v>
+        <v>66.54724551355373</v>
       </c>
       <c r="O8" t="n">
-        <v>8.119685559056929</v>
+        <v>8.157649509114359</v>
       </c>
       <c r="P8" t="n">
-        <v>347.80934184361</v>
+        <v>347.9524906999238</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34319,28 +34493,28 @@
         <v>0.0833</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2758256378391707</v>
+        <v>0.2634904056096344</v>
       </c>
       <c r="J9" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K9" t="n">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L9" t="n">
-        <v>0.074426967808498</v>
+        <v>0.06831137321735548</v>
       </c>
       <c r="M9" t="n">
-        <v>5.836659454013224</v>
+        <v>5.861715637131489</v>
       </c>
       <c r="N9" t="n">
-        <v>53.68910629079349</v>
+        <v>54.11121788309518</v>
       </c>
       <c r="O9" t="n">
-        <v>7.327285055925795</v>
+        <v>7.356032754351708</v>
       </c>
       <c r="P9" t="n">
-        <v>351.3359735767658</v>
+        <v>351.4583471996359</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34397,28 +34571,28 @@
         <v>0.0867</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2859534530133855</v>
+        <v>0.2740725369974849</v>
       </c>
       <c r="J10" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K10" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1033650313182781</v>
+        <v>0.09542149149942336</v>
       </c>
       <c r="M10" t="n">
-        <v>5.098202517714297</v>
+        <v>5.12310176053093</v>
       </c>
       <c r="N10" t="n">
-        <v>40.18499198856045</v>
+        <v>40.62677511199285</v>
       </c>
       <c r="O10" t="n">
-        <v>6.339163350834276</v>
+        <v>6.373913641711257</v>
       </c>
       <c r="P10" t="n">
-        <v>355.1449271151308</v>
+        <v>355.2628622217167</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34475,28 +34649,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2360998093541173</v>
+        <v>0.2263886317917446</v>
       </c>
       <c r="J11" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K11" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07237104619731416</v>
+        <v>0.06702450128976811</v>
       </c>
       <c r="M11" t="n">
-        <v>5.040957359139057</v>
+        <v>5.060365471301205</v>
       </c>
       <c r="N11" t="n">
-        <v>40.47919633576164</v>
+        <v>40.7030658492681</v>
       </c>
       <c r="O11" t="n">
-        <v>6.36232633049906</v>
+        <v>6.379895441875838</v>
       </c>
       <c r="P11" t="n">
-        <v>355.7437868829318</v>
+        <v>355.8401839495535</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34553,28 +34727,28 @@
         <v>0.0506</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4626710078907418</v>
+        <v>0.4506130200029921</v>
       </c>
       <c r="J12" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K12" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1956649386174476</v>
+        <v>0.1873030874582587</v>
       </c>
       <c r="M12" t="n">
-        <v>5.500026707360471</v>
+        <v>5.528785637568045</v>
       </c>
       <c r="N12" t="n">
-        <v>49.8539674643401</v>
+        <v>50.26577596467681</v>
       </c>
       <c r="O12" t="n">
-        <v>7.060734201507667</v>
+        <v>7.089836102807794</v>
       </c>
       <c r="P12" t="n">
-        <v>347.0430299507647</v>
+        <v>347.1627216831197</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34631,28 +34805,28 @@
         <v>0.0723</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6868494363385812</v>
+        <v>0.6814925017804803</v>
       </c>
       <c r="J13" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K13" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2522876146668862</v>
+        <v>0.2513473872475442</v>
       </c>
       <c r="M13" t="n">
-        <v>6.878735668942551</v>
+        <v>6.868538625702792</v>
       </c>
       <c r="N13" t="n">
-        <v>78.01205330529319</v>
+        <v>77.73091787733669</v>
       </c>
       <c r="O13" t="n">
-        <v>8.832443224006209</v>
+        <v>8.816513929968959</v>
       </c>
       <c r="P13" t="n">
-        <v>339.2548598229504</v>
+        <v>339.3087225786867</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34690,7 +34864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N570"/>
+  <dimension ref="A1:N573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75705,6 +75879,222 @@
         </is>
       </c>
     </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>-34.961688699149924,173.67017794862218</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>-34.96166164383798,173.67107765110165</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>-34.96175111819856,173.67201636737337</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>-34.961496756040354,173.6728896097665</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>-34.96121445715324,173.6737365527341</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>-34.960916284095575,173.67457700437976</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>-34.96056291494854,173.67537188274386</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>-34.96014320658377,173.6761266786304</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>-34.9596733090045,173.67683818533024</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>-34.95912095007094,173.67746434354723</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>-34.958515471227905,173.67803114165244</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>-34.95780589626103,173.67831628491678</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>-34.961696512445535,173.670178802611</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>-34.961668819017795,173.6710785550242</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>-34.961743961767944,173.67201459394195</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>-34.96149202668488,173.67288779632435</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>-34.96121082119376,173.67373462408912</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>-34.960911224225896,173.67457363344587</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>-34.960560500632695,173.67537017147774</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>-34.960140212679796,173.67612423540726</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>-34.95966769922833,173.67683216768845</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>-34.959116459947246,173.67745748571198</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>-34.958510083792454,173.6780184960492</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>-34.957802619317555,173.67830596373057</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>-34.961696512445535,173.670178802611</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>-34.961668819017795,173.6710785550242</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>-34.961743961767944,173.67201459394195</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>-34.96149202668488,173.67288779632435</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>-34.96121222599629,173.6737353692474</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>-34.96091011737938,173.67457289605414</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>-34.96055489318934,173.67536619692459</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>-34.960140212679796,173.67612423540726</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>-34.95966769922833,173.67683216768845</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>-34.959116459947246,173.67745748571198</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>-34.958510083792454,173.6780184960492</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>-34.957802619317555,173.67830596373057</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0036/nzd0036.xlsx
+++ b/data/nzd0036/nzd0036.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N573"/>
+  <dimension ref="A1:N577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27940,6 +27940,198 @@
         <v>352.71</v>
       </c>
       <c r="N573" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>359.51</v>
+      </c>
+      <c r="C574" t="n">
+        <v>356.62</v>
+      </c>
+      <c r="D574" t="n">
+        <v>339.16</v>
+      </c>
+      <c r="E574" t="n">
+        <v>343.08</v>
+      </c>
+      <c r="F574" t="n">
+        <v>347.93</v>
+      </c>
+      <c r="G574" t="n">
+        <v>341.19</v>
+      </c>
+      <c r="H574" t="n">
+        <v>342.08</v>
+      </c>
+      <c r="I574" t="n">
+        <v>345.53</v>
+      </c>
+      <c r="J574" t="n">
+        <v>351.21</v>
+      </c>
+      <c r="K574" t="n">
+        <v>353.88</v>
+      </c>
+      <c r="L574" t="n">
+        <v>349.52</v>
+      </c>
+      <c r="M574" t="n">
+        <v>353.41</v>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>359.51</v>
+      </c>
+      <c r="C575" t="n">
+        <v>356.4</v>
+      </c>
+      <c r="D575" t="n">
+        <v>339.33</v>
+      </c>
+      <c r="E575" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="F575" t="n">
+        <v>347.91</v>
+      </c>
+      <c r="G575" t="n">
+        <v>341.36</v>
+      </c>
+      <c r="H575" t="n">
+        <v>342</v>
+      </c>
+      <c r="I575" t="n">
+        <v>345.45</v>
+      </c>
+      <c r="J575" t="n">
+        <v>351.16</v>
+      </c>
+      <c r="K575" t="n">
+        <v>353.69</v>
+      </c>
+      <c r="L575" t="n">
+        <v>349.47</v>
+      </c>
+      <c r="M575" t="n">
+        <v>353.12</v>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>361.09</v>
+      </c>
+      <c r="C576" t="n">
+        <v>357.35</v>
+      </c>
+      <c r="D576" t="n">
+        <v>340.64</v>
+      </c>
+      <c r="E576" t="n">
+        <v>344.39</v>
+      </c>
+      <c r="F576" t="n">
+        <v>348.95</v>
+      </c>
+      <c r="G576" t="n">
+        <v>342.38</v>
+      </c>
+      <c r="H576" t="n">
+        <v>342.83</v>
+      </c>
+      <c r="I576" t="n">
+        <v>346.44</v>
+      </c>
+      <c r="J576" t="n">
+        <v>352.11</v>
+      </c>
+      <c r="K576" t="n">
+        <v>354.34</v>
+      </c>
+      <c r="L576" t="n">
+        <v>350.57</v>
+      </c>
+      <c r="M576" t="n">
+        <v>353.9</v>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>361.48</v>
+      </c>
+      <c r="C577" t="n">
+        <v>357.57</v>
+      </c>
+      <c r="D577" t="n">
+        <v>341.88</v>
+      </c>
+      <c r="E577" t="n">
+        <v>345.37</v>
+      </c>
+      <c r="F577" t="n">
+        <v>350.23</v>
+      </c>
+      <c r="G577" t="n">
+        <v>343.46</v>
+      </c>
+      <c r="H577" t="n">
+        <v>343.88</v>
+      </c>
+      <c r="I577" t="n">
+        <v>347.76</v>
+      </c>
+      <c r="J577" t="n">
+        <v>353.38</v>
+      </c>
+      <c r="K577" t="n">
+        <v>355.43</v>
+      </c>
+      <c r="L577" t="n">
+        <v>351.12</v>
+      </c>
+      <c r="M577" t="n">
+        <v>354.81</v>
+      </c>
+      <c r="N577" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -27956,7 +28148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B582"/>
+  <dimension ref="A1:B586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33779,6 +33971,46 @@
       </c>
       <c r="B582" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>-0.01</v>
       </c>
     </row>
   </sheetData>
@@ -33947,28 +34179,28 @@
         <v>0.07480000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3103690912288594</v>
+        <v>0.2933707085595987</v>
       </c>
       <c r="J2" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="K2" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1436498374845279</v>
+        <v>0.1286521064046536</v>
       </c>
       <c r="M2" t="n">
-        <v>4.454057097358781</v>
+        <v>4.524300803275609</v>
       </c>
       <c r="N2" t="n">
-        <v>32.76305720923868</v>
+        <v>33.56388402190424</v>
       </c>
       <c r="O2" t="n">
-        <v>5.723902271111788</v>
+        <v>5.793434561803925</v>
       </c>
       <c r="P2" t="n">
-        <v>364.4624560365594</v>
+        <v>364.631683534337</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34025,28 +34257,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4840271394562704</v>
+        <v>0.475416899933334</v>
       </c>
       <c r="J3" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="K3" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="L3" t="n">
-        <v>0.390214461856736</v>
+        <v>0.382531434324154</v>
       </c>
       <c r="M3" t="n">
-        <v>3.460756112859869</v>
+        <v>3.484263172002722</v>
       </c>
       <c r="N3" t="n">
-        <v>20.88788325288658</v>
+        <v>21.00685238955064</v>
       </c>
       <c r="O3" t="n">
-        <v>4.570326383628043</v>
+        <v>4.58332329097028</v>
       </c>
       <c r="P3" t="n">
-        <v>350.4009360612212</v>
+        <v>350.4866551715936</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34103,28 +34335,28 @@
         <v>0.1005</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4530561758558001</v>
+        <v>0.4302734443751106</v>
       </c>
       <c r="J4" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="K4" t="n">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1161966356917317</v>
+        <v>0.1055929520017003</v>
       </c>
       <c r="M4" t="n">
-        <v>7.702595765033617</v>
+        <v>7.774821608528655</v>
       </c>
       <c r="N4" t="n">
-        <v>88.62194501769247</v>
+        <v>89.83756204399928</v>
       </c>
       <c r="O4" t="n">
-        <v>9.413922934552442</v>
+        <v>9.478267882055206</v>
       </c>
       <c r="P4" t="n">
-        <v>344.6503103255982</v>
+        <v>344.8780355267425</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34181,28 +34413,28 @@
         <v>0.1076</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4544490314446161</v>
+        <v>0.4327554968661649</v>
       </c>
       <c r="J5" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="K5" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1341083216941211</v>
+        <v>0.1225303716175831</v>
       </c>
       <c r="M5" t="n">
-        <v>7.125055181574965</v>
+        <v>7.1806438224791</v>
       </c>
       <c r="N5" t="n">
-        <v>76.07806326224346</v>
+        <v>77.22137962419126</v>
       </c>
       <c r="O5" t="n">
-        <v>8.722273973124409</v>
+        <v>8.787569608497634</v>
       </c>
       <c r="P5" t="n">
-        <v>347.6690706406049</v>
+        <v>347.8850428013371</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34259,28 +34491,28 @@
         <v>0.0897</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4292489121799142</v>
+        <v>0.4093678855341124</v>
       </c>
       <c r="J6" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="K6" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1349010089637369</v>
+        <v>0.1237073140648939</v>
       </c>
       <c r="M6" t="n">
-        <v>6.526424140940757</v>
+        <v>6.571048893952298</v>
       </c>
       <c r="N6" t="n">
-        <v>67.41402527906888</v>
+        <v>68.35107926560384</v>
       </c>
       <c r="O6" t="n">
-        <v>8.210604440543271</v>
+        <v>8.267471152994961</v>
       </c>
       <c r="P6" t="n">
-        <v>351.7618290489261</v>
+        <v>351.9597555358223</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34337,28 +34569,28 @@
         <v>0.0914</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3861541303717587</v>
+        <v>0.3658651302256565</v>
       </c>
       <c r="J7" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="K7" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1162167343395519</v>
+        <v>0.1049804624643598</v>
       </c>
       <c r="M7" t="n">
-        <v>6.345126355629898</v>
+        <v>6.401074189642089</v>
       </c>
       <c r="N7" t="n">
-        <v>64.69634123437916</v>
+        <v>65.70979337649651</v>
       </c>
       <c r="O7" t="n">
-        <v>8.043403585198194</v>
+        <v>8.106157744363017</v>
       </c>
       <c r="P7" t="n">
-        <v>346.5365446213379</v>
+        <v>346.7385332963756</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34415,28 +34647,28 @@
         <v>0.0832</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3144962917613515</v>
+        <v>0.2957055548867524</v>
       </c>
       <c r="J8" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="K8" t="n">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07828483247491103</v>
+        <v>0.06966800748429547</v>
       </c>
       <c r="M8" t="n">
-        <v>6.441535284924391</v>
+        <v>6.48857646068767</v>
       </c>
       <c r="N8" t="n">
-        <v>66.54724551355373</v>
+        <v>67.34065434765422</v>
       </c>
       <c r="O8" t="n">
-        <v>8.157649509114359</v>
+        <v>8.206135165085586</v>
       </c>
       <c r="P8" t="n">
-        <v>347.9524906999238</v>
+        <v>348.139455400381</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34493,28 +34725,28 @@
         <v>0.0833</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2634904056096344</v>
+        <v>0.246692134991281</v>
       </c>
       <c r="J9" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="K9" t="n">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06831137321735548</v>
+        <v>0.06025011220912935</v>
       </c>
       <c r="M9" t="n">
-        <v>5.861715637131489</v>
+        <v>5.899626033147031</v>
       </c>
       <c r="N9" t="n">
-        <v>54.11121788309518</v>
+        <v>54.7417692772295</v>
       </c>
       <c r="O9" t="n">
-        <v>7.356032754351708</v>
+        <v>7.398768091867017</v>
       </c>
       <c r="P9" t="n">
-        <v>351.4583471996359</v>
+        <v>351.62548428473</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34571,28 +34803,28 @@
         <v>0.0867</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2740725369974849</v>
+        <v>0.2594684695668056</v>
       </c>
       <c r="J10" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="K10" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09542149149942336</v>
+        <v>0.08617827930532473</v>
       </c>
       <c r="M10" t="n">
-        <v>5.12310176053093</v>
+        <v>5.15123075432315</v>
       </c>
       <c r="N10" t="n">
-        <v>40.62677511199285</v>
+        <v>41.10520953944622</v>
       </c>
       <c r="O10" t="n">
-        <v>6.373913641711257</v>
+        <v>6.411334458554336</v>
       </c>
       <c r="P10" t="n">
-        <v>355.2628622217167</v>
+        <v>355.4082513922577</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34649,28 +34881,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2263886317917446</v>
+        <v>0.2160162004734132</v>
       </c>
       <c r="J11" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="K11" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06702450128976811</v>
+        <v>0.0617782172747271</v>
       </c>
       <c r="M11" t="n">
-        <v>5.060365471301205</v>
+        <v>5.074265041928298</v>
       </c>
       <c r="N11" t="n">
-        <v>40.7030658492681</v>
+        <v>40.8043828492728</v>
       </c>
       <c r="O11" t="n">
-        <v>6.379895441875838</v>
+        <v>6.387830840690195</v>
       </c>
       <c r="P11" t="n">
-        <v>355.8401839495535</v>
+        <v>355.9434453215454</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34727,28 +34959,28 @@
         <v>0.0506</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4506130200029921</v>
+        <v>0.438274726904601</v>
       </c>
       <c r="J12" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="K12" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1873030874582587</v>
+        <v>0.1797826478116714</v>
       </c>
       <c r="M12" t="n">
-        <v>5.528785637568045</v>
+        <v>5.550753608664713</v>
       </c>
       <c r="N12" t="n">
-        <v>50.26577596467681</v>
+        <v>50.45893312830643</v>
       </c>
       <c r="O12" t="n">
-        <v>7.089836102807794</v>
+        <v>7.103445159097551</v>
       </c>
       <c r="P12" t="n">
-        <v>347.1627216831197</v>
+        <v>347.2855549549582</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34805,28 +35037,28 @@
         <v>0.0723</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6814925017804803</v>
+        <v>0.6765434073274482</v>
       </c>
       <c r="J13" t="n">
+        <v>576</v>
+      </c>
+      <c r="K13" t="n">
         <v>572</v>
       </c>
-      <c r="K13" t="n">
-        <v>568</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.2513473872475442</v>
+        <v>0.251445562919922</v>
       </c>
       <c r="M13" t="n">
-        <v>6.868538625702792</v>
+        <v>6.844534608107195</v>
       </c>
       <c r="N13" t="n">
-        <v>77.73091787733669</v>
+        <v>77.27502334113312</v>
       </c>
       <c r="O13" t="n">
-        <v>8.816513929968959</v>
+        <v>8.790621328503072</v>
       </c>
       <c r="P13" t="n">
-        <v>339.3087225786867</v>
+        <v>339.3586258495275</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34864,7 +35096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N573"/>
+  <dimension ref="A1:N577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76095,6 +76327,294 @@
         </is>
       </c>
     </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>-34.96171420462058,173.67018073635643</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>-34.96167742923356,173.67107963973152</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>-34.96174873272169,173.67201577622953</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>-34.961505956786326,173.6728931377364</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>-34.96122784409462,173.67374365365583</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>-34.9609284594066,173.67458511569117</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>-34.960565251383215,173.67537353880795</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>-34.96015173920981,173.67613364181727</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>-34.95967114619927,173.67683586527545</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>-34.95911180144349,173.67745037070873</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>-34.958504903564794,173.67800633681685</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>-34.95780034816809,173.67829881043366</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>-34.96171420462058,173.67018073635643</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>-34.961679402408,173.6710798883103</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>-34.961747230754774,173.6720154040279</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>-34.96150449498556,173.67289257721774</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>-34.961228009365506,173.67374374132154</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>-34.96092711537879,173.67458422028653</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>-34.96056587443244,173.67537398042506</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>-34.960152337990564,173.67613413046203</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>-34.95967148413758,173.676836227784</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>-34.959112867848006,173.67745199944434</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>-34.95850511077392,173.6780068231861</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>-34.95780128907292,173.67830177394234</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>-34.96170001495736,173.67017918543362</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>-34.96167088188199,173.67107881490196</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>-34.96173565677434,173.67201253588613</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>-34.96149469232161,173.67288881844624</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>-34.96121941527973,173.67373918270485</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>-34.960919051211775,173.6745788478594</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>-34.9605594102965,173.67536939864792</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>-34.960144928078535,173.67612808348375</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>-34.959665063309295,173.67682934012208</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>-34.95910921962195,173.6774464274542</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>-34.958500552172595,173.67799612306283</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>-34.957798758363225,173.67829380312605</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>-34.961696512445535,173.670178802611</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>-34.961668908707544,173.67107856632322</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>-34.96172470125078,173.67200982100465</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>-34.96148626547002,173.67288558722234</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>-34.961208837943126,173.673733572101</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>-34.96091051268171,173.67457315940834</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>-34.960551232774854,173.67536360242488</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>-34.96013504819531,173.67612002084778</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>-34.95965647967504,173.6768201324073</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>-34.959103101826884,173.67743708365654</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>-34.95849827287158,173.67799077300165</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>-34.957795805867896,173.678284503841</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0036/nzd0036.xlsx
+++ b/data/nzd0036/nzd0036.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N577"/>
+  <dimension ref="A1:N579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28134,6 +28134,102 @@
       <c r="N577" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>360.14</v>
+      </c>
+      <c r="C578" t="n">
+        <v>357.05</v>
+      </c>
+      <c r="D578" t="n">
+        <v>341.78</v>
+      </c>
+      <c r="E578" t="n">
+        <v>345.13</v>
+      </c>
+      <c r="F578" t="n">
+        <v>349.93</v>
+      </c>
+      <c r="G578" t="n">
+        <v>342.54</v>
+      </c>
+      <c r="H578" t="n">
+        <v>343.28</v>
+      </c>
+      <c r="I578" t="n">
+        <v>347.43</v>
+      </c>
+      <c r="J578" t="n">
+        <v>353.07</v>
+      </c>
+      <c r="K578" t="n">
+        <v>355.3</v>
+      </c>
+      <c r="L578" t="n">
+        <v>352.26</v>
+      </c>
+      <c r="M578" t="n">
+        <v>353.46</v>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>358.72</v>
+      </c>
+      <c r="C579" t="n">
+        <v>356.3</v>
+      </c>
+      <c r="D579" t="n">
+        <v>346.25</v>
+      </c>
+      <c r="E579" t="n">
+        <v>347.85</v>
+      </c>
+      <c r="F579" t="n">
+        <v>352.18</v>
+      </c>
+      <c r="G579" t="n">
+        <v>345.3</v>
+      </c>
+      <c r="H579" t="n">
+        <v>346.37</v>
+      </c>
+      <c r="I579" t="n">
+        <v>349.59</v>
+      </c>
+      <c r="J579" t="n">
+        <v>355.18</v>
+      </c>
+      <c r="K579" t="n">
+        <v>357.34</v>
+      </c>
+      <c r="L579" t="n">
+        <v>356.85</v>
+      </c>
+      <c r="M579" t="n">
+        <v>358.64</v>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28148,7 +28244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B586"/>
+  <dimension ref="A1:B588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34011,6 +34107,26 @@
       </c>
       <c r="B586" t="n">
         <v>-0.01</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -34179,28 +34295,28 @@
         <v>0.07480000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2933707085595987</v>
+        <v>0.2844199457346015</v>
       </c>
       <c r="J2" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K2" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1286521064046536</v>
+        <v>0.1208881413193652</v>
       </c>
       <c r="M2" t="n">
-        <v>4.524300803275609</v>
+        <v>4.562367291060303</v>
       </c>
       <c r="N2" t="n">
-        <v>33.56388402190424</v>
+        <v>34.02623155050273</v>
       </c>
       <c r="O2" t="n">
-        <v>5.793434561803925</v>
+        <v>5.833200798061278</v>
       </c>
       <c r="P2" t="n">
-        <v>364.631683534337</v>
+        <v>364.7211160595187</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34257,28 +34373,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.475416899933334</v>
+        <v>0.4709862550056804</v>
       </c>
       <c r="J3" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K3" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L3" t="n">
-        <v>0.382531434324154</v>
+        <v>0.3784116912307768</v>
       </c>
       <c r="M3" t="n">
-        <v>3.484263172002722</v>
+        <v>3.496694227607335</v>
       </c>
       <c r="N3" t="n">
-        <v>21.00685238955064</v>
+        <v>21.07599439178646</v>
       </c>
       <c r="O3" t="n">
-        <v>4.58332329097028</v>
+        <v>4.590859874989266</v>
       </c>
       <c r="P3" t="n">
-        <v>350.4866551715936</v>
+        <v>350.5309247891087</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34335,28 +34451,28 @@
         <v>0.1005</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4302734443751106</v>
+        <v>0.4217760977476004</v>
       </c>
       <c r="J4" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K4" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1055929520017003</v>
+        <v>0.102074186655942</v>
       </c>
       <c r="M4" t="n">
-        <v>7.774821608528655</v>
+        <v>7.795951476591682</v>
       </c>
       <c r="N4" t="n">
-        <v>89.83756204399928</v>
+        <v>90.05993190670355</v>
       </c>
       <c r="O4" t="n">
-        <v>9.478267882055206</v>
+        <v>9.489991143657804</v>
       </c>
       <c r="P4" t="n">
-        <v>344.8780355267425</v>
+        <v>344.9632485723636</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34413,28 +34529,28 @@
         <v>0.1076</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4327554968661649</v>
+        <v>0.4238806631246472</v>
       </c>
       <c r="J5" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K5" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1225303716175831</v>
+        <v>0.1182035822408279</v>
       </c>
       <c r="M5" t="n">
-        <v>7.1806438224791</v>
+        <v>7.199346462074947</v>
       </c>
       <c r="N5" t="n">
-        <v>77.22137962419126</v>
+        <v>77.52793535822599</v>
       </c>
       <c r="O5" t="n">
-        <v>8.787569608497634</v>
+        <v>8.804994909608181</v>
       </c>
       <c r="P5" t="n">
-        <v>347.8850428013371</v>
+        <v>347.973696371505</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34491,28 +34607,28 @@
         <v>0.0897</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4093678855341124</v>
+        <v>0.4012592586877403</v>
       </c>
       <c r="J6" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K6" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1237073140648939</v>
+        <v>0.1195406811208513</v>
       </c>
       <c r="M6" t="n">
-        <v>6.571048893952298</v>
+        <v>6.585013134703211</v>
       </c>
       <c r="N6" t="n">
-        <v>68.35107926560384</v>
+        <v>68.59256094030779</v>
       </c>
       <c r="O6" t="n">
-        <v>8.267471152994961</v>
+        <v>8.28206260181048</v>
       </c>
       <c r="P6" t="n">
-        <v>351.9597555358223</v>
+        <v>352.0407563700085</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34569,28 +34685,28 @@
         <v>0.0914</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3658651302256565</v>
+        <v>0.357235102726064</v>
       </c>
       <c r="J7" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K7" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1049804624643598</v>
+        <v>0.1005551253015261</v>
       </c>
       <c r="M7" t="n">
-        <v>6.401074189642089</v>
+        <v>6.421247638565381</v>
       </c>
       <c r="N7" t="n">
-        <v>65.70979337649651</v>
+        <v>66.02553218702081</v>
       </c>
       <c r="O7" t="n">
-        <v>8.106157744363017</v>
+        <v>8.12560965017523</v>
       </c>
       <c r="P7" t="n">
-        <v>346.7385332963756</v>
+        <v>346.8247408296848</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34647,28 +34763,28 @@
         <v>0.0832</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2957055548867524</v>
+        <v>0.2880184037368035</v>
       </c>
       <c r="J8" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K8" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06966800748429547</v>
+        <v>0.0664252844139912</v>
       </c>
       <c r="M8" t="n">
-        <v>6.48857646068767</v>
+        <v>6.503527520679303</v>
       </c>
       <c r="N8" t="n">
-        <v>67.34065434765422</v>
+        <v>67.54213631759499</v>
       </c>
       <c r="O8" t="n">
-        <v>8.206135165085586</v>
+        <v>8.218402297137503</v>
       </c>
       <c r="P8" t="n">
-        <v>348.139455400381</v>
+        <v>348.2161972069381</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34725,28 +34841,28 @@
         <v>0.0833</v>
       </c>
       <c r="I9" t="n">
-        <v>0.246692134991281</v>
+        <v>0.2400367779615281</v>
       </c>
       <c r="J9" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K9" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06025011220912935</v>
+        <v>0.0573388244087123</v>
       </c>
       <c r="M9" t="n">
-        <v>5.899626033147031</v>
+        <v>5.910856397976491</v>
       </c>
       <c r="N9" t="n">
-        <v>54.7417692772295</v>
+        <v>54.87582589647989</v>
       </c>
       <c r="O9" t="n">
-        <v>7.398768091867017</v>
+        <v>7.407821940117074</v>
       </c>
       <c r="P9" t="n">
-        <v>351.62548428473</v>
+        <v>351.6919280966088</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34803,28 +34919,28 @@
         <v>0.0867</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2594684695668056</v>
+        <v>0.2538384948503108</v>
       </c>
       <c r="J10" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K10" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08617827930532473</v>
+        <v>0.08296378617689559</v>
       </c>
       <c r="M10" t="n">
-        <v>5.15123075432315</v>
+        <v>5.15769668877304</v>
       </c>
       <c r="N10" t="n">
-        <v>41.10520953944622</v>
+        <v>41.19516124458386</v>
       </c>
       <c r="O10" t="n">
-        <v>6.411334458554336</v>
+        <v>6.418345678177817</v>
       </c>
       <c r="P10" t="n">
-        <v>355.4082513922577</v>
+        <v>355.4644891370083</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34881,28 +34997,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2160162004734132</v>
+        <v>0.2123269183528856</v>
       </c>
       <c r="J11" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K11" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0617782172747271</v>
+        <v>0.06012145607824515</v>
       </c>
       <c r="M11" t="n">
-        <v>5.074265041928298</v>
+        <v>5.07422651878184</v>
       </c>
       <c r="N11" t="n">
-        <v>40.8043828492728</v>
+        <v>40.764833684294</v>
       </c>
       <c r="O11" t="n">
-        <v>6.387830840690195</v>
+        <v>6.384734425510117</v>
       </c>
       <c r="P11" t="n">
-        <v>355.9434453215454</v>
+        <v>355.980294305628</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34959,28 +35075,28 @@
         <v>0.0506</v>
       </c>
       <c r="I12" t="n">
-        <v>0.438274726904601</v>
+        <v>0.4352760121228528</v>
       </c>
       <c r="J12" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K12" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1797826478116714</v>
+        <v>0.1786972406474208</v>
       </c>
       <c r="M12" t="n">
-        <v>5.550753608664713</v>
+        <v>5.546548135886276</v>
       </c>
       <c r="N12" t="n">
-        <v>50.45893312830643</v>
+        <v>50.36724774528474</v>
       </c>
       <c r="O12" t="n">
-        <v>7.103445159097551</v>
+        <v>7.09698863922472</v>
       </c>
       <c r="P12" t="n">
-        <v>347.2855549549582</v>
+        <v>347.3154920867211</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35037,28 +35153,28 @@
         <v>0.0723</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6765434073274482</v>
+        <v>0.6756672036833798</v>
       </c>
       <c r="J13" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K13" t="n">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L13" t="n">
-        <v>0.251445562919922</v>
+        <v>0.2524042015455414</v>
       </c>
       <c r="M13" t="n">
-        <v>6.844534608107195</v>
+        <v>6.829513249100597</v>
       </c>
       <c r="N13" t="n">
-        <v>77.27502334113312</v>
+        <v>77.03417684207663</v>
       </c>
       <c r="O13" t="n">
-        <v>8.790621328503072</v>
+        <v>8.776911577660824</v>
       </c>
       <c r="P13" t="n">
-        <v>339.3586258495275</v>
+        <v>339.3674669083088</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35096,7 +35212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N577"/>
+  <dimension ref="A1:N579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76615,6 +76731,150 @@
         </is>
       </c>
     </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>-34.9617085467169,173.67018011795042</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>-34.96167357257442,173.671079153873</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>-34.96172558476076,173.67201003994668</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>-34.961488329188775,173.67288637854242</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>-34.961211317006416,173.67373488708617</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>-34.96091778624439,173.67457800512585</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>-34.960555905644405,173.6753669145522</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>-34.96013751816618,173.67612203650657</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>-34.95965857489291,173.6768223799596</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>-34.95910383147222,173.67743819805435</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>-34.95849354850143,173.67797968378483</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>-34.95780018594312,173.6782982994839</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>-34.961721299452165,173.67018151181804</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>-34.96168029930548,173.67108000130065</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>-34.96168609186464,173.67200025324283</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>-34.96146494037572,173.6728774102506</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>-34.961192724031335,173.67372502469954</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>-34.96089596555573,173.6745634679759</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>-34.9605318403652,173.6753498571006</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>-34.960121351083565,173.67610884310568</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>-34.95964431389295,173.6768070821062</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>-34.95909238165213,173.6774207105832</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>-34.95847452668485,173.67793503510887</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>-34.95778337942365,173.67824536509912</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0036/nzd0036.xlsx
+++ b/data/nzd0036/nzd0036.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N579"/>
+  <dimension ref="A1:N583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28228,6 +28228,198 @@
         <v>358.64</v>
       </c>
       <c r="N579" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>358.92</v>
+      </c>
+      <c r="C580" t="n">
+        <v>356.61</v>
+      </c>
+      <c r="D580" t="n">
+        <v>348.44</v>
+      </c>
+      <c r="E580" t="n">
+        <v>349.61</v>
+      </c>
+      <c r="F580" t="n">
+        <v>354.02</v>
+      </c>
+      <c r="G580" t="n">
+        <v>346.55</v>
+      </c>
+      <c r="H580" t="n">
+        <v>347.89</v>
+      </c>
+      <c r="I580" t="n">
+        <v>350.57</v>
+      </c>
+      <c r="J580" t="n">
+        <v>356.36</v>
+      </c>
+      <c r="K580" t="n">
+        <v>358.48</v>
+      </c>
+      <c r="L580" t="n">
+        <v>358.36</v>
+      </c>
+      <c r="M580" t="n">
+        <v>357.44</v>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>359.07</v>
+      </c>
+      <c r="C581" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="D581" t="n">
+        <v>348.54</v>
+      </c>
+      <c r="E581" t="n">
+        <v>349.91</v>
+      </c>
+      <c r="F581" t="n">
+        <v>353.71</v>
+      </c>
+      <c r="G581" t="n">
+        <v>346.53</v>
+      </c>
+      <c r="H581" t="n">
+        <v>347.81</v>
+      </c>
+      <c r="I581" t="n">
+        <v>350.33</v>
+      </c>
+      <c r="J581" t="n">
+        <v>356</v>
+      </c>
+      <c r="K581" t="n">
+        <v>358.23</v>
+      </c>
+      <c r="L581" t="n">
+        <v>358.06</v>
+      </c>
+      <c r="M581" t="n">
+        <v>357.58</v>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>361.02</v>
+      </c>
+      <c r="C582" t="n">
+        <v>356.83</v>
+      </c>
+      <c r="D582" t="n">
+        <v>350.03</v>
+      </c>
+      <c r="E582" t="n">
+        <v>351.86</v>
+      </c>
+      <c r="F582" t="n">
+        <v>354.98</v>
+      </c>
+      <c r="G582" t="n">
+        <v>348.72</v>
+      </c>
+      <c r="H582" t="n">
+        <v>350.05</v>
+      </c>
+      <c r="I582" t="n">
+        <v>351.87</v>
+      </c>
+      <c r="J582" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="K582" t="n">
+        <v>358.21</v>
+      </c>
+      <c r="L582" t="n">
+        <v>357.18</v>
+      </c>
+      <c r="M582" t="n">
+        <v>355.1</v>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>361.81</v>
+      </c>
+      <c r="C583" t="n">
+        <v>356.77</v>
+      </c>
+      <c r="D583" t="n">
+        <v>349.92</v>
+      </c>
+      <c r="E583" t="n">
+        <v>352.3</v>
+      </c>
+      <c r="F583" t="n">
+        <v>355.07</v>
+      </c>
+      <c r="G583" t="n">
+        <v>348.43</v>
+      </c>
+      <c r="H583" t="n">
+        <v>349.81</v>
+      </c>
+      <c r="I583" t="n">
+        <v>351.66</v>
+      </c>
+      <c r="J583" t="n">
+        <v>356.12</v>
+      </c>
+      <c r="K583" t="n">
+        <v>356.89</v>
+      </c>
+      <c r="L583" t="n">
+        <v>355.49</v>
+      </c>
+      <c r="M583" t="n">
+        <v>351.63</v>
+      </c>
+      <c r="N583" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28244,7 +28436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B588"/>
+  <dimension ref="A1:B592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34127,6 +34319,46 @@
       </c>
       <c r="B588" t="n">
         <v>0.22</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -34295,28 +34527,28 @@
         <v>0.07480000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2844199457346015</v>
+        <v>0.2678783527210669</v>
       </c>
       <c r="J2" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K2" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1208881413193652</v>
+        <v>0.1074737092071676</v>
       </c>
       <c r="M2" t="n">
-        <v>4.562367291060303</v>
+        <v>4.632936556064722</v>
       </c>
       <c r="N2" t="n">
-        <v>34.02623155050273</v>
+        <v>34.78757802864931</v>
       </c>
       <c r="O2" t="n">
-        <v>5.833200798061278</v>
+        <v>5.89809952685179</v>
       </c>
       <c r="P2" t="n">
-        <v>364.7211160595187</v>
+        <v>364.8875324213536</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34373,28 +34605,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4709862550056804</v>
+        <v>0.4622290152581843</v>
       </c>
       <c r="J3" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K3" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3784116912307768</v>
+        <v>0.3703237020402075</v>
       </c>
       <c r="M3" t="n">
-        <v>3.496694227607335</v>
+        <v>3.521262988451812</v>
       </c>
       <c r="N3" t="n">
-        <v>21.07599439178646</v>
+        <v>21.20705771791161</v>
       </c>
       <c r="O3" t="n">
-        <v>4.590859874989266</v>
+        <v>4.605112128701277</v>
       </c>
       <c r="P3" t="n">
-        <v>350.5309247891087</v>
+        <v>350.6190383068985</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34451,28 +34683,28 @@
         <v>0.1005</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4217760977476004</v>
+        <v>0.4121780584421263</v>
       </c>
       <c r="J4" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K4" t="n">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="L4" t="n">
-        <v>0.102074186655942</v>
+        <v>0.09903408853208884</v>
       </c>
       <c r="M4" t="n">
-        <v>7.795951476591682</v>
+        <v>7.796327108918713</v>
       </c>
       <c r="N4" t="n">
-        <v>90.05993190670355</v>
+        <v>89.77269050750469</v>
       </c>
       <c r="O4" t="n">
-        <v>9.489991143657804</v>
+        <v>9.474845144249308</v>
       </c>
       <c r="P4" t="n">
-        <v>344.9632485723636</v>
+        <v>345.0601927818855</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34529,28 +34761,28 @@
         <v>0.1076</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4238806631246472</v>
+        <v>0.4124453206150783</v>
       </c>
       <c r="J5" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K5" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1182035822408279</v>
+        <v>0.1136121106819071</v>
       </c>
       <c r="M5" t="n">
-        <v>7.199346462074947</v>
+        <v>7.205233485916793</v>
       </c>
       <c r="N5" t="n">
-        <v>77.52793535822599</v>
+        <v>77.47509563801989</v>
       </c>
       <c r="O5" t="n">
-        <v>8.804994909608181</v>
+        <v>8.801993844466145</v>
       </c>
       <c r="P5" t="n">
-        <v>347.973696371505</v>
+        <v>348.0887351091121</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34607,28 +34839,28 @@
         <v>0.0897</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4012592586877403</v>
+        <v>0.38990662658946</v>
       </c>
       <c r="J6" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K6" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1195406811208513</v>
+        <v>0.1145680819164593</v>
       </c>
       <c r="M6" t="n">
-        <v>6.585013134703211</v>
+        <v>6.59059952738617</v>
       </c>
       <c r="N6" t="n">
-        <v>68.59256094030779</v>
+        <v>68.58717854704423</v>
       </c>
       <c r="O6" t="n">
-        <v>8.28206260181048</v>
+        <v>8.281737652633307</v>
       </c>
       <c r="P6" t="n">
-        <v>352.0407563700085</v>
+        <v>352.1549755322481</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34685,28 +34917,28 @@
         <v>0.0914</v>
       </c>
       <c r="I7" t="n">
-        <v>0.357235102726064</v>
+        <v>0.3452062641880607</v>
       </c>
       <c r="J7" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K7" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1005551253015261</v>
+        <v>0.09522079268571348</v>
       </c>
       <c r="M7" t="n">
-        <v>6.421247638565381</v>
+        <v>6.436102752784532</v>
       </c>
       <c r="N7" t="n">
-        <v>66.02553218702081</v>
+        <v>66.099523541319</v>
       </c>
       <c r="O7" t="n">
-        <v>8.12560965017523</v>
+        <v>8.130161347803559</v>
       </c>
       <c r="P7" t="n">
-        <v>346.8247408296848</v>
+        <v>346.9457555678793</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34763,28 +34995,28 @@
         <v>0.0832</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2880184037368035</v>
+        <v>0.2784352184758253</v>
       </c>
       <c r="J8" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K8" t="n">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0664252844139912</v>
+        <v>0.06299898604611776</v>
       </c>
       <c r="M8" t="n">
-        <v>6.503527520679303</v>
+        <v>6.504753135537801</v>
       </c>
       <c r="N8" t="n">
-        <v>67.54213631759499</v>
+        <v>67.41577050715911</v>
       </c>
       <c r="O8" t="n">
-        <v>8.218402297137503</v>
+        <v>8.210710718759923</v>
       </c>
       <c r="P8" t="n">
-        <v>348.2161972069381</v>
+        <v>348.3125500520266</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34841,28 +35073,28 @@
         <v>0.0833</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2400367779615281</v>
+        <v>0.2304859253295842</v>
       </c>
       <c r="J9" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K9" t="n">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0573388244087123</v>
+        <v>0.05361020457279286</v>
       </c>
       <c r="M9" t="n">
-        <v>5.910856397976491</v>
+        <v>5.915886842438968</v>
       </c>
       <c r="N9" t="n">
-        <v>54.87582589647989</v>
+        <v>54.82997804619456</v>
       </c>
       <c r="O9" t="n">
-        <v>7.407821940117074</v>
+        <v>7.404726736767168</v>
       </c>
       <c r="P9" t="n">
-        <v>351.6919280966088</v>
+        <v>351.7879634031569</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34919,28 +35151,28 @@
         <v>0.0867</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2538384948503108</v>
+        <v>0.2457123356469231</v>
       </c>
       <c r="J10" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K10" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08296378617689559</v>
+        <v>0.07889055829438785</v>
       </c>
       <c r="M10" t="n">
-        <v>5.15769668877304</v>
+        <v>5.156796422197377</v>
       </c>
       <c r="N10" t="n">
-        <v>41.19516124458386</v>
+        <v>41.15004353791177</v>
       </c>
       <c r="O10" t="n">
-        <v>6.418345678177817</v>
+        <v>6.414829969524662</v>
       </c>
       <c r="P10" t="n">
-        <v>355.4644891370083</v>
+        <v>355.5462535956585</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34997,28 +35229,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2123269183528856</v>
+        <v>0.2072698622041602</v>
       </c>
       <c r="J11" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K11" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06012145607824515</v>
+        <v>0.05820425805996365</v>
       </c>
       <c r="M11" t="n">
-        <v>5.07422651878184</v>
+        <v>5.062929687584577</v>
       </c>
       <c r="N11" t="n">
-        <v>40.764833684294</v>
+        <v>40.5792911633349</v>
       </c>
       <c r="O11" t="n">
-        <v>6.384734425510117</v>
+        <v>6.370187686664726</v>
       </c>
       <c r="P11" t="n">
-        <v>355.980294305628</v>
+        <v>356.0311884819033</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35075,28 +35307,28 @@
         <v>0.0506</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4352760121228528</v>
+        <v>0.4329978060799231</v>
       </c>
       <c r="J12" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K12" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1786972406474208</v>
+        <v>0.1794406229887185</v>
       </c>
       <c r="M12" t="n">
-        <v>5.546548135886276</v>
+        <v>5.51969823433086</v>
       </c>
       <c r="N12" t="n">
-        <v>50.36724774528474</v>
+        <v>50.04847055810914</v>
       </c>
       <c r="O12" t="n">
-        <v>7.09698863922472</v>
+        <v>7.074494367663963</v>
       </c>
       <c r="P12" t="n">
-        <v>347.3154920867211</v>
+        <v>347.3384367137842</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35153,28 +35385,28 @@
         <v>0.0723</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6756672036833798</v>
+        <v>0.6729270543674341</v>
       </c>
       <c r="J13" t="n">
+        <v>582</v>
+      </c>
+      <c r="K13" t="n">
         <v>578</v>
       </c>
-      <c r="K13" t="n">
-        <v>574</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.2524042015455414</v>
+        <v>0.2537634397577136</v>
       </c>
       <c r="M13" t="n">
-        <v>6.829513249100597</v>
+        <v>6.796391401753526</v>
       </c>
       <c r="N13" t="n">
-        <v>77.03417684207663</v>
+        <v>76.56821278686917</v>
       </c>
       <c r="O13" t="n">
-        <v>8.776911577660824</v>
+        <v>8.750326438874676</v>
       </c>
       <c r="P13" t="n">
-        <v>339.3674669083088</v>
+        <v>339.3954372679624</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35212,7 +35444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N579"/>
+  <dimension ref="A1:N583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76875,6 +77107,294 @@
         </is>
       </c>
     </row>
+    <row r="580">
+      <c r="A580" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>-34.961719503292265,173.67018131549864</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>-34.96167751892331,173.67107965103054</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>-34.96166674299565,173.67199545841828</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>-34.96144980643742,173.67287160724104</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>-34.9611775191088,173.67371695946227</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>-34.96088608299685,173.6745568841243</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>-34.96052000242753,173.67534146638374</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>-34.9601140160178,173.67610285721253</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>-34.95963633854611,173.67679852691091</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>-34.95908598322213,173.67741093817494</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>-34.95846826895939,173.67792034676896</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>-34.95778727282792,173.67825762788905</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>-34.96171815617234,173.6701811682591</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>-34.961677877682305,173.67107969622668</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>-34.96166585948564,173.6719952394766</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>-34.96144722678882,173.67287061809188</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>-34.96118008080774,173.67371831827924</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>-34.96088624111779,173.6745569894659</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>-34.96052062547691,173.67534190800035</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>-34.96011581236046,173.67610432314544</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>-34.95963877170285,173.6768011369703</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>-34.95908738638667,173.67741308124678</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>-34.958469512216254,173.677923264982</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>-34.95778681859749,173.67825619723018</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>-34.96170064361332,173.67017925414538</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>-34.96167554574887,173.67107940245174</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>-34.96165269518647,173.67199197724577</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>-34.96143045907264,173.672864188624</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>-34.96116958610551,173.6737127515136</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>-34.96086892687371,173.67454545456175</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>-34.96050318009399,173.67532954273767</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>-34.96010428582802,173.67609491674366</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>-34.95963404056471,173.67679606185496</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>-34.95908749863983,173.67741325269256</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>-34.95847315910262,173.67793182507413</t>
+        </is>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>-34.95779486496265,173.67828154033273</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>-34.961693548781696,173.6701784786842</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>-34.961676083887355,173.67107947024596</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>-34.9616536670475,173.67199221808158</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>-34.961426675587894,173.67286273787263</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>-34.96116884238644,173.67371235701847</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>-34.96087121962755,173.67454698201453</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>-34.96050504924222,173.675330867587</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>-34.96010585762794,173.67609619943468</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>-34.9596379606506,173.6768002669505</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>-34.95909490734796,173.67742456811317</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>-34.95848016278038,173.67794826434408</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>-34.957806123375875,173.67831700024655</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0036/nzd0036.xlsx
+++ b/data/nzd0036/nzd0036.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N583"/>
+  <dimension ref="A1:N585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28420,6 +28420,102 @@
         <v>351.63</v>
       </c>
       <c r="N583" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="C584" t="n">
+        <v>356.81</v>
+      </c>
+      <c r="D584" t="n">
+        <v>350.07</v>
+      </c>
+      <c r="E584" t="n">
+        <v>352.76</v>
+      </c>
+      <c r="F584" t="n">
+        <v>355.26</v>
+      </c>
+      <c r="G584" t="n">
+        <v>348.71</v>
+      </c>
+      <c r="H584" t="n">
+        <v>350</v>
+      </c>
+      <c r="I584" t="n">
+        <v>351.83</v>
+      </c>
+      <c r="J584" t="n">
+        <v>356.53</v>
+      </c>
+      <c r="K584" t="n">
+        <v>357.13</v>
+      </c>
+      <c r="L584" t="n">
+        <v>355.46</v>
+      </c>
+      <c r="M584" t="n">
+        <v>351.81</v>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>363.34</v>
+      </c>
+      <c r="C585" t="n">
+        <v>357.51</v>
+      </c>
+      <c r="D585" t="n">
+        <v>351.34</v>
+      </c>
+      <c r="E585" t="n">
+        <v>354.18</v>
+      </c>
+      <c r="F585" t="n">
+        <v>356.42</v>
+      </c>
+      <c r="G585" t="n">
+        <v>349.83</v>
+      </c>
+      <c r="H585" t="n">
+        <v>350.92</v>
+      </c>
+      <c r="I585" t="n">
+        <v>352.82</v>
+      </c>
+      <c r="J585" t="n">
+        <v>357.34</v>
+      </c>
+      <c r="K585" t="n">
+        <v>357.63</v>
+      </c>
+      <c r="L585" t="n">
+        <v>356.67</v>
+      </c>
+      <c r="M585" t="n">
+        <v>350.92</v>
+      </c>
+      <c r="N585" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28436,7 +28532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B592"/>
+  <dimension ref="A1:B594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34359,6 +34455,26 @@
       </c>
       <c r="B592" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -34527,28 +34643,28 @@
         <v>0.07480000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2678783527210669</v>
+        <v>0.2615374048639484</v>
       </c>
       <c r="J2" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K2" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1074737092071676</v>
+        <v>0.102918714212158</v>
       </c>
       <c r="M2" t="n">
-        <v>4.632936556064722</v>
+        <v>4.657386123227139</v>
       </c>
       <c r="N2" t="n">
-        <v>34.78757802864931</v>
+        <v>34.96357641283645</v>
       </c>
       <c r="O2" t="n">
-        <v>5.89809952685179</v>
+        <v>5.913000626825305</v>
       </c>
       <c r="P2" t="n">
-        <v>364.8875324213536</v>
+        <v>364.9515697693536</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34605,28 +34721,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4622290152581843</v>
+        <v>0.4582544021556275</v>
       </c>
       <c r="J3" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K3" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3703237020402075</v>
+        <v>0.3668911133712199</v>
       </c>
       <c r="M3" t="n">
-        <v>3.521262988451812</v>
+        <v>3.531816119791833</v>
       </c>
       <c r="N3" t="n">
-        <v>21.20705771791161</v>
+        <v>21.25031113136388</v>
       </c>
       <c r="O3" t="n">
-        <v>4.605112128701277</v>
+        <v>4.609805975457522</v>
       </c>
       <c r="P3" t="n">
-        <v>350.6190383068985</v>
+        <v>350.6591782106644</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34683,28 +34799,28 @@
         <v>0.1005</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4121780584421263</v>
+        <v>0.408492578361317</v>
       </c>
       <c r="J4" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K4" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09903408853208884</v>
+        <v>0.0980506715755034</v>
       </c>
       <c r="M4" t="n">
-        <v>7.796327108918713</v>
+        <v>7.790265396370803</v>
       </c>
       <c r="N4" t="n">
-        <v>89.77269050750469</v>
+        <v>89.56466734564269</v>
       </c>
       <c r="O4" t="n">
-        <v>9.474845144249308</v>
+        <v>9.463861122482868</v>
       </c>
       <c r="P4" t="n">
-        <v>345.0601927818855</v>
+        <v>345.0975576148142</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34761,28 +34877,28 @@
         <v>0.1076</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4124453206150783</v>
+        <v>0.4085913054240621</v>
       </c>
       <c r="J5" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K5" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1136121106819071</v>
+        <v>0.1123879986782508</v>
       </c>
       <c r="M5" t="n">
-        <v>7.205233485916793</v>
+        <v>7.199221893814534</v>
       </c>
       <c r="N5" t="n">
-        <v>77.47509563801989</v>
+        <v>77.32007285756934</v>
       </c>
       <c r="O5" t="n">
-        <v>8.801993844466145</v>
+        <v>8.793183317636982</v>
       </c>
       <c r="P5" t="n">
-        <v>348.0887351091121</v>
+        <v>348.1276545191303</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34839,28 +34955,28 @@
         <v>0.0897</v>
       </c>
       <c r="I6" t="n">
-        <v>0.38990662658946</v>
+        <v>0.3853057880174885</v>
       </c>
       <c r="J6" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K6" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1145680819164593</v>
+        <v>0.1127520328406765</v>
       </c>
       <c r="M6" t="n">
-        <v>6.59059952738617</v>
+        <v>6.589157173906064</v>
       </c>
       <c r="N6" t="n">
-        <v>68.58717854704423</v>
+        <v>68.50818836685576</v>
       </c>
       <c r="O6" t="n">
-        <v>8.281737652633307</v>
+        <v>8.276967341173684</v>
       </c>
       <c r="P6" t="n">
-        <v>352.1549755322481</v>
+        <v>352.201438469269</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34917,28 +35033,28 @@
         <v>0.0914</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3452062641880607</v>
+        <v>0.3404964944561328</v>
       </c>
       <c r="J7" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K7" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09522079268571348</v>
+        <v>0.09334573933744084</v>
       </c>
       <c r="M7" t="n">
-        <v>6.436102752784532</v>
+        <v>6.437365981862797</v>
       </c>
       <c r="N7" t="n">
-        <v>66.099523541319</v>
+        <v>66.03638363775579</v>
       </c>
       <c r="O7" t="n">
-        <v>8.130161347803559</v>
+        <v>8.126277354222891</v>
       </c>
       <c r="P7" t="n">
-        <v>346.9457555678793</v>
+        <v>346.9933188160331</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34995,28 +35111,28 @@
         <v>0.0832</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2784352184758253</v>
+        <v>0.2748218569430057</v>
       </c>
       <c r="J8" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K8" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06299898604611776</v>
+        <v>0.06185352714696379</v>
       </c>
       <c r="M8" t="n">
-        <v>6.504753135537801</v>
+        <v>6.499709187532274</v>
       </c>
       <c r="N8" t="n">
-        <v>67.41577050715911</v>
+        <v>67.2808690253066</v>
       </c>
       <c r="O8" t="n">
-        <v>8.210710718759923</v>
+        <v>8.202491635186627</v>
       </c>
       <c r="P8" t="n">
-        <v>348.3125500520266</v>
+        <v>348.3490208519342</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35073,28 +35189,28 @@
         <v>0.0833</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2304859253295842</v>
+        <v>0.2266486836397808</v>
       </c>
       <c r="J9" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K9" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05361020457279286</v>
+        <v>0.05222810969939018</v>
       </c>
       <c r="M9" t="n">
-        <v>5.915886842438968</v>
+        <v>5.913873508504716</v>
       </c>
       <c r="N9" t="n">
-        <v>54.82997804619456</v>
+        <v>54.75058842612221</v>
       </c>
       <c r="O9" t="n">
-        <v>7.404726736767168</v>
+        <v>7.399364055520056</v>
       </c>
       <c r="P9" t="n">
-        <v>351.7879634031569</v>
+        <v>351.826693848154</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35151,28 +35267,28 @@
         <v>0.0867</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2457123356469231</v>
+        <v>0.2421765793045074</v>
       </c>
       <c r="J10" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K10" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07889055829438785</v>
+        <v>0.07721841580369615</v>
       </c>
       <c r="M10" t="n">
-        <v>5.156796422197377</v>
+        <v>5.154530504074776</v>
       </c>
       <c r="N10" t="n">
-        <v>41.15004353791177</v>
+        <v>41.10106708161789</v>
       </c>
       <c r="O10" t="n">
-        <v>6.414829969524662</v>
+        <v>6.411011393034479</v>
       </c>
       <c r="P10" t="n">
-        <v>355.5462535956585</v>
+        <v>355.5819607712267</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35229,28 +35345,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2072698622041602</v>
+        <v>0.2044111679247567</v>
       </c>
       <c r="J11" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K11" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05820425805996365</v>
+        <v>0.05704939571352274</v>
       </c>
       <c r="M11" t="n">
-        <v>5.062929687584577</v>
+        <v>5.058882540936088</v>
       </c>
       <c r="N11" t="n">
-        <v>40.5792911633349</v>
+        <v>40.50027001862899</v>
       </c>
       <c r="O11" t="n">
-        <v>6.370187686664726</v>
+        <v>6.363982245310635</v>
       </c>
       <c r="P11" t="n">
-        <v>356.0311884819033</v>
+        <v>356.0600586264592</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35307,28 +35423,28 @@
         <v>0.0506</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4329978060799231</v>
+        <v>0.4310437008662924</v>
       </c>
       <c r="J12" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K12" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1794406229887185</v>
+        <v>0.1791993920032641</v>
       </c>
       <c r="M12" t="n">
-        <v>5.51969823433086</v>
+        <v>5.510404075350055</v>
       </c>
       <c r="N12" t="n">
-        <v>50.04847055810914</v>
+        <v>49.9062029275793</v>
       </c>
       <c r="O12" t="n">
-        <v>7.074494367663963</v>
+        <v>7.064432243823937</v>
       </c>
       <c r="P12" t="n">
-        <v>347.3384367137842</v>
+        <v>347.3581684472664</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35385,28 +35501,28 @@
         <v>0.0723</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6729270543674341</v>
+        <v>0.6687488346213558</v>
       </c>
       <c r="J13" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K13" t="n">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2537634397577136</v>
+        <v>0.2526169161959073</v>
       </c>
       <c r="M13" t="n">
-        <v>6.796391401753526</v>
+        <v>6.793043459627167</v>
       </c>
       <c r="N13" t="n">
-        <v>76.56821278686917</v>
+        <v>76.42981698351066</v>
       </c>
       <c r="O13" t="n">
-        <v>8.750326438874676</v>
+        <v>8.742414825636603</v>
       </c>
       <c r="P13" t="n">
-        <v>339.3954372679624</v>
+        <v>339.4381771863015</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35444,7 +35560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N583"/>
+  <dimension ref="A1:N585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77395,6 +77511,150 @@
         </is>
       </c>
     </row>
+    <row r="584">
+      <c r="A584" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>-34.96169049530984,173.67017814494145</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>-34.96167572512836,173.67107942504984</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>-34.96165234178246,173.67199188966913</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>-34.96142272012657,173.67286122117818</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>-34.96116727231284,173.6737115241954</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>-34.96086900593418,173.67454550723255</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>-34.96050356949988,173.67532981874797</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>-34.96010458521849,173.67609516106577</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>-34.95963518955543,173.67679729438294</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>-34.959093560310194,173.67742251076382</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>-34.958480287106,173.67794855616543</t>
+        </is>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>-34.957805539366234,173.67831516082717</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>-34.961679808158365,173.67017697684201</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>-34.96166944684603,173.67107863411744</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>-34.96164112120524,173.67198910911085</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>-34.96141050978925,173.67285653920928</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>-34.96115768660025,173.67370643959214</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>-34.960860151160475,173.67453960810533</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>-34.9604964044315,173.67532474015943</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>-34.96009717530438,173.67608911409457</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>-34.9596297149525,173.67679142174998</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>-34.959090753981414,173.67741822461954</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>-34.95847527263876,173.67793678603695</t>
+        </is>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>-34.95780842696923,173.6783242557344</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0036/nzd0036.xlsx
+++ b/data/nzd0036/nzd0036.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N585"/>
+  <dimension ref="A1:N589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28516,6 +28516,198 @@
         <v>350.92</v>
       </c>
       <c r="N585" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>364.93</v>
+      </c>
+      <c r="C586" t="n">
+        <v>357.71</v>
+      </c>
+      <c r="D586" t="n">
+        <v>351.47</v>
+      </c>
+      <c r="E586" t="n">
+        <v>354.66</v>
+      </c>
+      <c r="F586" t="n">
+        <v>356.44</v>
+      </c>
+      <c r="G586" t="n">
+        <v>350.08</v>
+      </c>
+      <c r="H586" t="n">
+        <v>350.39</v>
+      </c>
+      <c r="I586" t="n">
+        <v>352.47</v>
+      </c>
+      <c r="J586" t="n">
+        <v>357.11</v>
+      </c>
+      <c r="K586" t="n">
+        <v>357.47</v>
+      </c>
+      <c r="L586" t="n">
+        <v>357.46</v>
+      </c>
+      <c r="M586" t="n">
+        <v>349.8</v>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>365.52</v>
+      </c>
+      <c r="C587" t="n">
+        <v>358</v>
+      </c>
+      <c r="D587" t="n">
+        <v>351.45</v>
+      </c>
+      <c r="E587" t="n">
+        <v>355.14</v>
+      </c>
+      <c r="F587" t="n">
+        <v>356.68</v>
+      </c>
+      <c r="G587" t="n">
+        <v>350.69</v>
+      </c>
+      <c r="H587" t="n">
+        <v>350.48</v>
+      </c>
+      <c r="I587" t="n">
+        <v>352.62</v>
+      </c>
+      <c r="J587" t="n">
+        <v>357.17</v>
+      </c>
+      <c r="K587" t="n">
+        <v>357.28</v>
+      </c>
+      <c r="L587" t="n">
+        <v>358.21</v>
+      </c>
+      <c r="M587" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>366.76</v>
+      </c>
+      <c r="C588" t="n">
+        <v>358.7</v>
+      </c>
+      <c r="D588" t="n">
+        <v>350.99</v>
+      </c>
+      <c r="E588" t="n">
+        <v>354.73</v>
+      </c>
+      <c r="F588" t="n">
+        <v>356.99</v>
+      </c>
+      <c r="G588" t="n">
+        <v>350.39</v>
+      </c>
+      <c r="H588" t="n">
+        <v>349.66</v>
+      </c>
+      <c r="I588" t="n">
+        <v>352.23</v>
+      </c>
+      <c r="J588" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="K588" t="n">
+        <v>356.41</v>
+      </c>
+      <c r="L588" t="n">
+        <v>357.09</v>
+      </c>
+      <c r="M588" t="n">
+        <v>347.84</v>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="C589" t="n">
+        <v>358.99</v>
+      </c>
+      <c r="D589" t="n">
+        <v>351.11</v>
+      </c>
+      <c r="E589" t="n">
+        <v>354.5</v>
+      </c>
+      <c r="F589" t="n">
+        <v>357.23</v>
+      </c>
+      <c r="G589" t="n">
+        <v>350.47</v>
+      </c>
+      <c r="H589" t="n">
+        <v>349.84</v>
+      </c>
+      <c r="I589" t="n">
+        <v>352.61</v>
+      </c>
+      <c r="J589" t="n">
+        <v>356.76</v>
+      </c>
+      <c r="K589" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="L589" t="n">
+        <v>356.6</v>
+      </c>
+      <c r="M589" t="n">
+        <v>347.84</v>
+      </c>
+      <c r="N589" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28532,7 +28724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B594"/>
+  <dimension ref="A1:B598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34475,6 +34667,46 @@
       </c>
       <c r="B594" t="n">
         <v>0.09</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -34643,28 +34875,28 @@
         <v>0.07480000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2615374048639484</v>
+        <v>0.253768370329597</v>
       </c>
       <c r="J2" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="K2" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="L2" t="n">
-        <v>0.102918714212158</v>
+        <v>0.09830288795193631</v>
       </c>
       <c r="M2" t="n">
-        <v>4.657386123227139</v>
+        <v>4.675040430105808</v>
       </c>
       <c r="N2" t="n">
-        <v>34.96357641283645</v>
+        <v>34.95581855443496</v>
       </c>
       <c r="O2" t="n">
-        <v>5.913000626825305</v>
+        <v>5.912344590298755</v>
       </c>
       <c r="P2" t="n">
-        <v>364.9515697693536</v>
+        <v>365.0303557216959</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34721,28 +34953,28 @@
         <v>0.0789</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4582544021556275</v>
+        <v>0.4520449057653671</v>
       </c>
       <c r="J3" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="K3" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3668911133712199</v>
+        <v>0.3626740662077829</v>
       </c>
       <c r="M3" t="n">
-        <v>3.531816119791833</v>
+        <v>3.543173678484468</v>
       </c>
       <c r="N3" t="n">
-        <v>21.25031113136388</v>
+        <v>21.2499709793582</v>
       </c>
       <c r="O3" t="n">
-        <v>4.609805975457522</v>
+        <v>4.609769080914814</v>
       </c>
       <c r="P3" t="n">
-        <v>350.6591782106644</v>
+        <v>350.7221507171776</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34799,28 +35031,28 @@
         <v>0.1005</v>
       </c>
       <c r="I4" t="n">
-        <v>0.408492578361317</v>
+        <v>0.4019891303563943</v>
       </c>
       <c r="J4" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="K4" t="n">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0980506715755034</v>
+        <v>0.09647814840082281</v>
       </c>
       <c r="M4" t="n">
-        <v>7.790265396370803</v>
+        <v>7.773309015564382</v>
       </c>
       <c r="N4" t="n">
-        <v>89.56466734564269</v>
+        <v>89.10971352416362</v>
       </c>
       <c r="O4" t="n">
-        <v>9.463861122482868</v>
+        <v>9.439794146281137</v>
       </c>
       <c r="P4" t="n">
-        <v>345.0975576148142</v>
+        <v>345.1637752800405</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34877,28 +35109,28 @@
         <v>0.1076</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4085913054240621</v>
+        <v>0.4027491816026472</v>
       </c>
       <c r="J5" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="K5" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1123879986782508</v>
+        <v>0.1109445801076812</v>
       </c>
       <c r="M5" t="n">
-        <v>7.199221893814534</v>
+        <v>7.178228021144398</v>
       </c>
       <c r="N5" t="n">
-        <v>77.32007285756934</v>
+        <v>76.92051251716548</v>
       </c>
       <c r="O5" t="n">
-        <v>8.793183317636982</v>
+        <v>8.770433998221836</v>
       </c>
       <c r="P5" t="n">
-        <v>348.1276545191303</v>
+        <v>348.1869053332347</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34955,28 +35187,28 @@
         <v>0.0897</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3853057880174885</v>
+        <v>0.3776259600128569</v>
       </c>
       <c r="J6" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="K6" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1127520328406765</v>
+        <v>0.1100227990033074</v>
       </c>
       <c r="M6" t="n">
-        <v>6.589157173906064</v>
+        <v>6.579867758831471</v>
       </c>
       <c r="N6" t="n">
-        <v>68.50818836685576</v>
+        <v>68.26057930821884</v>
       </c>
       <c r="O6" t="n">
-        <v>8.276967341173684</v>
+        <v>8.261996084979636</v>
       </c>
       <c r="P6" t="n">
-        <v>352.201438469269</v>
+        <v>352.2793242902925</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35033,28 +35265,28 @@
         <v>0.0914</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3404964944561328</v>
+        <v>0.3327952641192857</v>
       </c>
       <c r="J7" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="K7" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09334573933744084</v>
+        <v>0.09057386073448415</v>
       </c>
       <c r="M7" t="n">
-        <v>6.437365981862797</v>
+        <v>6.431682724711288</v>
       </c>
       <c r="N7" t="n">
-        <v>66.03638363775579</v>
+        <v>65.80651933743418</v>
       </c>
       <c r="O7" t="n">
-        <v>8.126277354222891</v>
+        <v>8.112121753119474</v>
       </c>
       <c r="P7" t="n">
-        <v>346.9933188160331</v>
+        <v>347.0714232368428</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35111,28 +35343,28 @@
         <v>0.0832</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2748218569430057</v>
+        <v>0.2672506584012065</v>
       </c>
       <c r="J8" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="K8" t="n">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06185352714696379</v>
+        <v>0.05939556867225859</v>
       </c>
       <c r="M8" t="n">
-        <v>6.499709187532274</v>
+        <v>6.492006788680878</v>
       </c>
       <c r="N8" t="n">
-        <v>67.2808690253066</v>
+        <v>67.03536052203856</v>
       </c>
       <c r="O8" t="n">
-        <v>8.202491635186627</v>
+        <v>8.187512474618806</v>
       </c>
       <c r="P8" t="n">
-        <v>348.3490208519342</v>
+        <v>348.4257682364756</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35189,28 +35421,28 @@
         <v>0.0833</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2266486836397808</v>
+        <v>0.219354433020855</v>
       </c>
       <c r="J9" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="K9" t="n">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05222810969939018</v>
+        <v>0.04965871368944996</v>
       </c>
       <c r="M9" t="n">
-        <v>5.913873508504716</v>
+        <v>5.907788162731677</v>
       </c>
       <c r="N9" t="n">
-        <v>54.75058842612221</v>
+        <v>54.57457578907127</v>
       </c>
       <c r="O9" t="n">
-        <v>7.399364055520056</v>
+        <v>7.387460713199852</v>
       </c>
       <c r="P9" t="n">
-        <v>351.826693848154</v>
+        <v>351.9006321145264</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35267,28 +35499,28 @@
         <v>0.0867</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2421765793045074</v>
+        <v>0.2352555332578399</v>
       </c>
       <c r="J10" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="K10" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07721841580369615</v>
+        <v>0.07397467940365743</v>
       </c>
       <c r="M10" t="n">
-        <v>5.154530504074776</v>
+        <v>5.149455003132007</v>
       </c>
       <c r="N10" t="n">
-        <v>41.10106708161789</v>
+        <v>40.99865005105502</v>
       </c>
       <c r="O10" t="n">
-        <v>6.411011393034479</v>
+        <v>6.403018823262588</v>
       </c>
       <c r="P10" t="n">
-        <v>355.5819607712267</v>
+        <v>355.6521542535912</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35345,28 +35577,28 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2044111679247567</v>
+        <v>0.1982063878872485</v>
       </c>
       <c r="J11" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="K11" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05704939571352274</v>
+        <v>0.05445371959518719</v>
       </c>
       <c r="M11" t="n">
-        <v>5.058882540936088</v>
+        <v>5.05336550707371</v>
       </c>
       <c r="N11" t="n">
-        <v>40.50027001862899</v>
+        <v>40.36831545504405</v>
       </c>
       <c r="O11" t="n">
-        <v>6.363982245310635</v>
+        <v>6.353606491988944</v>
       </c>
       <c r="P11" t="n">
-        <v>356.0600586264592</v>
+        <v>356.1229894054662</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35423,28 +35655,28 @@
         <v>0.0506</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4310437008662924</v>
+        <v>0.4288882815914176</v>
       </c>
       <c r="J12" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="K12" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1791993920032641</v>
+        <v>0.1800063325441351</v>
       </c>
       <c r="M12" t="n">
-        <v>5.510404075350055</v>
+        <v>5.483341828004381</v>
       </c>
       <c r="N12" t="n">
-        <v>49.9062029275793</v>
+        <v>49.58623889566394</v>
       </c>
       <c r="O12" t="n">
-        <v>7.064432243823937</v>
+        <v>7.041749704133479</v>
       </c>
       <c r="P12" t="n">
-        <v>347.3581684472664</v>
+        <v>347.3800315154501</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35501,28 +35733,28 @@
         <v>0.0723</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6687488346213558</v>
+        <v>0.657151434213206</v>
       </c>
       <c r="J13" t="n">
+        <v>588</v>
+      </c>
+      <c r="K13" t="n">
         <v>584</v>
       </c>
-      <c r="K13" t="n">
-        <v>580</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.2526169161959073</v>
+        <v>0.2478355294727389</v>
       </c>
       <c r="M13" t="n">
-        <v>6.793043459627167</v>
+        <v>6.801457304573135</v>
       </c>
       <c r="N13" t="n">
-        <v>76.42981698351066</v>
+        <v>76.40043100364095</v>
       </c>
       <c r="O13" t="n">
-        <v>8.742414825636603</v>
+        <v>8.740734008287916</v>
       </c>
       <c r="P13" t="n">
-        <v>339.4381771863015</v>
+        <v>339.5572973708047</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35560,7 +35792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N585"/>
+  <dimension ref="A1:N589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77655,6 +77887,294 @@
         </is>
       </c>
     </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>-34.961665528686986,173.67017541610466</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>-34.961667653051066,173.6710784081368</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>-34.96163997264221,173.67198882448682</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>-34.961406382351235,173.67285495657222</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>-34.961157521329326,173.67370635192657</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>-34.96085817464845,173.67453829133606</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>-34.96050053213396,173.67532766586794</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>-34.96009979497101,173.67609125191254</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>-34.95963126946941,173.67679308928766</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>-34.959091652006634,173.6774195961857</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>-34.95847199872975,173.67792910140838</t>
+        </is>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>-34.95781206080572,173.67833570101186</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>-34.96166023001522,173.67017483696327</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>-34.96166505204838,173.67107808046484</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>-34.96164014934422,173.67198886827512</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>-34.96140225491319,173.6728533739353</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>-34.96115553807842,173.67370529993985</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>-34.96085335195903,173.67453507841924</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>-34.96049983120336,173.67532716904947</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>-34.96009867225674,173.67609033570486</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>-34.95963086394327,173.67679265427782</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>-34.95909271841158,173.67742122492052</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>-34.95846889058783,173.67792180587546</t>
+        </is>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>-34.95781108745676,173.67833263531244</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>-34.96164909382366,173.67017361978503</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>-34.961658773766025,173.6710772895327</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>-34.96164421349032,173.67198987540638</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>-34.96140578043319,173.672854725771</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>-34.96115297637931,173.67370394112373</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>-34.960855723773506,173.67453665854222</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>-34.96050621745987,173.67533169561787</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>-34.96010159131384,173.67609271784497</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>-34.95963404056471,173.67679606185496</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>-34.95909760142337,173.6774286828121</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>-34.9584735320796,173.67793270053815</t>
+        </is>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>-34.95781842001696,173.67835573024976</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>-34.96164199899192,173.6701728443249</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>-34.96165617276334,173.67107696186082</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>-34.96164315327829,173.67198961267647</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>-34.9614077581639,173.6728554841179</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>-34.961150993128385,173.6737028891371</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>-34.96085509128964,173.67453623717608</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>-34.96050481559869,173.67533070198084</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>-34.96009874710437,173.67609039678533</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>-34.95963363503858,173.6767956268451</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>-34.95909670339825,173.67742731124576</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>-34.95847556273193,173.67793746695344</t>
+        </is>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>-34.95781842001696,173.67835573024976</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
